--- a/datos/prueba.xlsx
+++ b/datos/prueba.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Documents\Trabajo\generacion_actas\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DBEF82-3E80-4E2C-AAFB-C198C144AF38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32AAC81-AF29-4F75-A988-DF10E363B241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{6AF58E88-A706-4C6B-B8F9-989A40A8C736}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{6AF58E88-A706-4C6B-B8F9-989A40A8C736}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="262">
   <si>
     <t>año</t>
   </si>
@@ -76,12 +76,6 @@
     <t>25 de mayo</t>
   </si>
   <si>
-    <t>EX-2023-11681699- -GDEBA-DGAMAMGP</t>
-  </si>
-  <si>
-    <t>ACTA-2023-48249740-GDEBA-SSRSUYECMAMGP</t>
-  </si>
-  <si>
     <t>Guillotina</t>
   </si>
   <si>
@@ -133,21 +127,12 @@
     <t>Retro</t>
   </si>
   <si>
-    <t>EX-2023-14841018- -GDEBA-DGAMAMGP</t>
-  </si>
-  <si>
-    <t>IF-2025-03114841-GDEBA-SSTAYLMAMGP</t>
-  </si>
-  <si>
     <t>Prefactibilidad Ceamse</t>
   </si>
   <si>
     <t>Contratación / Servicio</t>
   </si>
   <si>
-    <t>RS-2023-24751930-GDEBA-MAMGP</t>
-  </si>
-  <si>
     <t>Carta Acuerdo 1 - CEAMSE</t>
   </si>
   <si>
@@ -166,9 +151,6 @@
     <t>Camiones (Caja Abierta)</t>
   </si>
   <si>
-    <t>ACTA-2023-48250050-GDEBA-DPRSUMAMGP</t>
-  </si>
-  <si>
     <t>Chalecos II</t>
   </si>
   <si>
@@ -196,24 +178,12 @@
     <t>Alberti</t>
   </si>
   <si>
-    <t>EX-2023-26736633- -GDEBA-DGAMAMGP</t>
-  </si>
-  <si>
-    <t>ACTA-2023-31475701-GDEBA-DPRSUMAMGP</t>
-  </si>
-  <si>
     <t>Minicargadora I</t>
   </si>
   <si>
     <t>Minicargadora</t>
   </si>
   <si>
-    <t>EX-2023-16385859- -GDEBA-DGAMAMGP</t>
-  </si>
-  <si>
-    <t>DOCFI-2023-28064179-GDEBA-DGPTGP</t>
-  </si>
-  <si>
     <t>Transferencias</t>
   </si>
   <si>
@@ -223,12 +193,6 @@
     <t>Almirante Brown</t>
   </si>
   <si>
-    <t>EX-2023-00967510- -GDEBA-DGAMAMGP</t>
-  </si>
-  <si>
-    <t>IF-2023-19099764-GDEBA-SSRSUYECMAMGP</t>
-  </si>
-  <si>
     <t>Enfardadora I</t>
   </si>
   <si>
@@ -241,24 +205,12 @@
     <t>Compostera / Contenedor</t>
   </si>
   <si>
-    <t>ACTA-2023-50950851-GDEBA-SSRSUYECMAMGP</t>
-  </si>
-  <si>
-    <t>IF-2023-44382338-GDEBA-SSTAYLMAMGP</t>
-  </si>
-  <si>
     <t>Camiones (Volquete)PNUD 1</t>
   </si>
   <si>
     <t>Camiones (Volquete)</t>
   </si>
   <si>
-    <t>IF-2025-13443538-GDEBA-SSTAYLMAMGP</t>
-  </si>
-  <si>
-    <t>ACTA-2023-50950455-GDEBA-SSRSUYECMAMGP</t>
-  </si>
-  <si>
     <t>Autoelevador II</t>
   </si>
   <si>
@@ -815,6 +767,51 @@
   </si>
   <si>
     <t>aut_2025_venc</t>
+  </si>
+  <si>
+    <t>ACTA-2023-156123-GDEBA-SSRSUYECMAMGP</t>
+  </si>
+  <si>
+    <t>IF-2022-561561-GDEBA-SSTAYLMAMGP</t>
+  </si>
+  <si>
+    <t>RS-2023-1561561-GDEBA-MAMGP</t>
+  </si>
+  <si>
+    <t>ACTA-2023-3336889-GDEBA-DPRSUMAMGP</t>
+  </si>
+  <si>
+    <t>ACTA-2025-314751111-GDEBA-DPRSUMAMGP</t>
+  </si>
+  <si>
+    <t>DOCFI-2023-156156-GDEBA-DGPTGP</t>
+  </si>
+  <si>
+    <t>IF-2023-37888-GDEBA-SSRSUYECMAMGP</t>
+  </si>
+  <si>
+    <t>ACTA-2023-33336-GDEBA-SSRSUYECMAMGP</t>
+  </si>
+  <si>
+    <t>IF-2023-77778-GDEBA-SSTAYLMAMGP</t>
+  </si>
+  <si>
+    <t>ACTA-2023-9999992-GDEBA-SSRSUYECMAMGP</t>
+  </si>
+  <si>
+    <t>EX-2023-123456- -GDEBA-DGAMAMGP</t>
+  </si>
+  <si>
+    <t>EX-2023-789456- -GDEBA-DGAMAMGP</t>
+  </si>
+  <si>
+    <t>EX-2023-123789- -GDEBA-DGAMAMGP</t>
+  </si>
+  <si>
+    <t>EX-2023-159678- -GDEBA-DGAMAMGP</t>
+  </si>
+  <si>
+    <t>EX-2023-369741- -GDEBA-DGAMAMGP</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +1186,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1251,10 +1248,10 @@
         <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>247</v>
       </c>
       <c r="G2" s="1">
         <v>45021</v>
@@ -1263,28 +1260,28 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2">
+        <v>1922000</v>
+      </c>
+      <c r="L2">
+        <v>1922000</v>
+      </c>
+      <c r="M2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
+      <c r="N2" t="s">
         <v>19</v>
       </c>
-      <c r="K2">
-        <v>3844000</v>
-      </c>
-      <c r="L2">
-        <v>3844000</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>20</v>
       </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" t="s">
-        <v>22</v>
-      </c>
       <c r="P2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -1301,10 +1298,10 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>247</v>
       </c>
       <c r="G3" s="1">
         <v>45021</v>
@@ -1313,28 +1310,28 @@
         <v>105</v>
       </c>
       <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3">
+        <v>1536.85</v>
+      </c>
+      <c r="L3">
+        <v>161369.25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
         <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3">
-        <v>3073.7</v>
-      </c>
-      <c r="L3">
-        <v>322738.5</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -1351,10 +1348,10 @@
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>247</v>
       </c>
       <c r="G4" s="1">
         <v>45021</v>
@@ -1363,28 +1360,28 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4">
+        <v>182444</v>
+      </c>
+      <c r="L4">
+        <v>182444</v>
+      </c>
+      <c r="M4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" t="s">
         <v>19</v>
       </c>
-      <c r="K4">
-        <v>364888</v>
-      </c>
-      <c r="L4">
-        <v>364888</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="O4" t="s">
         <v>20</v>
       </c>
-      <c r="N4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" t="s">
-        <v>22</v>
-      </c>
       <c r="P4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1401,10 +1398,10 @@
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>247</v>
       </c>
       <c r="G5" s="1">
         <v>45021</v>
@@ -1413,28 +1410,28 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5">
+        <v>2999435</v>
+      </c>
+      <c r="L5">
+        <v>3028878.5</v>
+      </c>
+      <c r="M5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
       </c>
-      <c r="J5" t="s">
+      <c r="P5" t="s">
         <v>29</v>
-      </c>
-      <c r="K5">
-        <v>5998870</v>
-      </c>
-      <c r="L5">
-        <v>6057757</v>
-      </c>
-      <c r="M5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" t="s">
-        <v>30</v>
-      </c>
-      <c r="P5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -1451,10 +1448,10 @@
         <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>247</v>
       </c>
       <c r="G6" s="1">
         <v>45021</v>
@@ -1463,28 +1460,28 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6">
+        <v>21803953.969999999</v>
+      </c>
+      <c r="L6">
+        <v>21803953.969999999</v>
+      </c>
+      <c r="M6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" t="s">
         <v>32</v>
-      </c>
-      <c r="J6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6">
-        <v>43607907.939999998</v>
-      </c>
-      <c r="L6">
-        <v>43607907.939999998</v>
-      </c>
-      <c r="M6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" t="s">
-        <v>33</v>
-      </c>
-      <c r="P6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1501,10 +1498,10 @@
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>258</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>248</v>
       </c>
       <c r="G7" s="1">
         <v>45132</v>
@@ -1513,28 +1510,28 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K7">
-        <v>1039000</v>
+        <v>519500</v>
       </c>
       <c r="L7">
-        <v>1039000</v>
+        <v>519500</v>
       </c>
       <c r="M7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1551,10 +1548,10 @@
         <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>258</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>249</v>
       </c>
       <c r="G8" s="1">
         <v>45132</v>
@@ -1563,28 +1560,28 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K8">
-        <v>16684841.25</v>
+        <v>8342420.625</v>
       </c>
       <c r="L8">
-        <v>16684841.25</v>
+        <v>8342420.625</v>
       </c>
       <c r="M8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="P8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1601,10 +1598,10 @@
         <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G9" s="1">
         <v>45267</v>
@@ -1613,28 +1610,28 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K9">
-        <v>53259669.340000004</v>
+        <v>26629834.670000002</v>
       </c>
       <c r="L9">
-        <v>53259669.340000004</v>
+        <v>26629834.670000002</v>
       </c>
       <c r="M9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O9" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P9" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1651,10 +1648,10 @@
         <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>250</v>
       </c>
       <c r="G10" s="1">
         <v>45168</v>
@@ -1663,28 +1660,28 @@
         <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K10">
-        <v>1220</v>
+        <v>610</v>
       </c>
       <c r="L10">
-        <v>54900</v>
+        <v>27450</v>
       </c>
       <c r="M10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="P10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1701,10 +1698,10 @@
         <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>250</v>
       </c>
       <c r="G11" s="1">
         <v>45168</v>
@@ -1713,28 +1710,28 @@
         <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K11">
-        <v>346.06</v>
+        <v>173.03</v>
       </c>
       <c r="L11">
-        <v>15572.7</v>
+        <v>7786.35</v>
       </c>
       <c r="M11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="P11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1751,10 +1748,10 @@
         <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>250</v>
       </c>
       <c r="G12" s="1">
         <v>45168</v>
@@ -1763,28 +1760,28 @@
         <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="J12" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12">
+        <v>412.5</v>
+      </c>
+      <c r="L12">
+        <v>18562.5</v>
+      </c>
+      <c r="M12" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" t="s">
+        <v>43</v>
+      </c>
+      <c r="P12" t="s">
         <v>48</v>
-      </c>
-      <c r="K12">
-        <v>825</v>
-      </c>
-      <c r="L12">
-        <v>37125</v>
-      </c>
-      <c r="M12" t="s">
-        <v>20</v>
-      </c>
-      <c r="N12" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" t="s">
-        <v>49</v>
-      </c>
-      <c r="P12" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1795,16 +1792,16 @@
         <v>2023</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>259</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>251</v>
       </c>
       <c r="G13" s="1">
         <v>45105</v>
@@ -1813,28 +1810,28 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="J13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13">
+        <v>6739403.9550000001</v>
+      </c>
+      <c r="L13">
+        <v>6739403.9550000001</v>
+      </c>
+      <c r="M13" t="s">
+        <v>49</v>
+      </c>
+      <c r="N13" t="s">
         <v>19</v>
       </c>
-      <c r="K13">
-        <v>13478807.91</v>
-      </c>
-      <c r="L13">
-        <v>13478807.91</v>
-      </c>
-      <c r="M13" t="s">
-        <v>55</v>
-      </c>
-      <c r="N13" t="s">
-        <v>21</v>
-      </c>
       <c r="O13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P13" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1845,16 +1842,16 @@
         <v>2023</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>259</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>251</v>
       </c>
       <c r="G14" s="1">
         <v>45105</v>
@@ -1863,28 +1860,28 @@
         <v>65</v>
       </c>
       <c r="I14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14">
+        <v>1536.85</v>
+      </c>
+      <c r="L14">
+        <v>99895.25</v>
+      </c>
+      <c r="M14" t="s">
+        <v>49</v>
+      </c>
+      <c r="N14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14" t="s">
+        <v>20</v>
+      </c>
+      <c r="P14" t="s">
         <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14">
-        <v>3073.7</v>
-      </c>
-      <c r="L14">
-        <v>199790.5</v>
-      </c>
-      <c r="M14" t="s">
-        <v>55</v>
-      </c>
-      <c r="N14" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" t="s">
-        <v>22</v>
-      </c>
-      <c r="P14" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1895,16 +1892,16 @@
         <v>2023</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>252</v>
       </c>
       <c r="G15" s="1">
         <v>45111</v>
@@ -1913,28 +1910,28 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="J15" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K15">
-        <v>6500000</v>
+        <v>3250000</v>
       </c>
       <c r="L15">
-        <v>6500000</v>
+        <v>3250000</v>
       </c>
       <c r="M15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="N15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O15" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="P15" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1945,16 +1942,16 @@
         <v>2022</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>253</v>
       </c>
       <c r="G16" s="1">
         <v>44901</v>
@@ -1963,28 +1960,28 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="J16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16">
+        <v>1747500</v>
+      </c>
+      <c r="L16">
+        <v>1747500</v>
+      </c>
+      <c r="M16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" t="s">
         <v>19</v>
       </c>
-      <c r="K16">
-        <v>3495000</v>
-      </c>
-      <c r="L16">
-        <v>3495000</v>
-      </c>
-      <c r="M16" t="s">
-        <v>64</v>
-      </c>
-      <c r="N16" t="s">
-        <v>21</v>
-      </c>
       <c r="O16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P16" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1995,16 +1992,16 @@
         <v>2022</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E17" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>253</v>
       </c>
       <c r="G17" s="1">
         <v>44901</v>
@@ -2013,28 +2010,28 @@
         <v>300</v>
       </c>
       <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17">
+        <v>1536.85</v>
+      </c>
+      <c r="L17">
+        <v>461055</v>
+      </c>
+      <c r="M17" t="s">
+        <v>54</v>
+      </c>
+      <c r="N17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O17" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" t="s">
         <v>23</v>
-      </c>
-      <c r="J17" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17">
-        <v>3073.7</v>
-      </c>
-      <c r="L17">
-        <v>922110</v>
-      </c>
-      <c r="M17" t="s">
-        <v>64</v>
-      </c>
-      <c r="N17" t="s">
-        <v>21</v>
-      </c>
-      <c r="O17" t="s">
-        <v>22</v>
-      </c>
-      <c r="P17" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -2045,16 +2042,16 @@
         <v>2022</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>253</v>
       </c>
       <c r="G18" s="1">
         <v>44901</v>
@@ -2063,28 +2060,28 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18">
+        <v>182444</v>
+      </c>
+      <c r="L18">
+        <v>182444</v>
+      </c>
+      <c r="M18" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" t="s">
         <v>19</v>
       </c>
-      <c r="K18">
-        <v>364888</v>
-      </c>
-      <c r="L18">
-        <v>364888</v>
-      </c>
-      <c r="M18" t="s">
-        <v>64</v>
-      </c>
-      <c r="N18" t="s">
-        <v>21</v>
-      </c>
       <c r="O18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -2095,16 +2092,16 @@
         <v>2022</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>253</v>
       </c>
       <c r="G19" s="1">
         <v>44901</v>
@@ -2113,28 +2110,28 @@
         <v>26</v>
       </c>
       <c r="I19" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="K19">
-        <v>9752</v>
+        <v>4876</v>
       </c>
       <c r="L19">
-        <v>253552</v>
+        <v>126776</v>
       </c>
       <c r="M19" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="N19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P19" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -2145,16 +2142,16 @@
         <v>2022</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="F20" t="s">
-        <v>71</v>
+        <v>254</v>
       </c>
       <c r="G20" s="1">
         <v>44901</v>
@@ -2163,28 +2160,28 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="J20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20">
+        <v>6739403.9550000001</v>
+      </c>
+      <c r="L20">
+        <v>6739403.9550000001</v>
+      </c>
+      <c r="M20" t="s">
+        <v>54</v>
+      </c>
+      <c r="N20" t="s">
         <v>19</v>
       </c>
-      <c r="K20">
-        <v>13478807.91</v>
-      </c>
-      <c r="L20">
-        <v>13478807.91</v>
-      </c>
-      <c r="M20" t="s">
-        <v>64</v>
-      </c>
-      <c r="N20" t="s">
-        <v>21</v>
-      </c>
       <c r="O20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P20" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -2195,16 +2192,16 @@
         <v>2023</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="F21" t="s">
-        <v>72</v>
+        <v>255</v>
       </c>
       <c r="G21" s="1">
         <v>45194</v>
@@ -2213,28 +2210,28 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="J21" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K21">
-        <v>97328231.980000004</v>
+        <v>48664115.990000002</v>
       </c>
       <c r="L21">
-        <v>97328231.980000004</v>
+        <v>48664115.990000002</v>
       </c>
       <c r="M21" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="N21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O21" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P21" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -2245,16 +2242,16 @@
         <v>2024</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="F22" t="s">
-        <v>75</v>
+        <v>255</v>
       </c>
       <c r="G22" s="1">
         <v>45301</v>
@@ -2263,28 +2260,28 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J22" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K22">
-        <v>53259669.340000004</v>
+        <v>26629834.670000002</v>
       </c>
       <c r="L22">
-        <v>53259669.340000004</v>
+        <v>26629834.670000002</v>
       </c>
       <c r="M22" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="N22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O22" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P22" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -2295,16 +2292,16 @@
         <v>2023</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E23" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="F23" t="s">
-        <v>76</v>
+        <v>256</v>
       </c>
       <c r="G23" s="1">
         <v>45202</v>
@@ -2313,28 +2310,28 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="J23" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23">
+        <v>6571690</v>
+      </c>
+      <c r="L23">
+        <v>6571690</v>
+      </c>
+      <c r="M23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N23" t="s">
         <v>19</v>
       </c>
-      <c r="K23">
-        <v>13143380</v>
-      </c>
-      <c r="L23">
-        <v>13143380</v>
-      </c>
-      <c r="M23" t="s">
-        <v>64</v>
-      </c>
-      <c r="N23" t="s">
-        <v>21</v>
-      </c>
       <c r="O23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P23" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2359,66 +2356,66 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E1" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F1" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="G1" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="H1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="I1" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="J1" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="K1" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="L1" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="M1" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="N1" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="O1" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="P1" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="Q1" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="R1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="S1" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="T1" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B2">
         <v>301234567</v>
@@ -2427,52 +2424,52 @@
         <v>123456</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H2">
         <v>46023</v>
       </c>
       <c r="I2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="J2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L2">
         <v>46023</v>
       </c>
       <c r="M2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="N2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P2">
         <v>46023</v>
       </c>
       <c r="Q2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="R2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T2">
         <v>46023</v>
@@ -2480,7 +2477,7 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="B3">
         <v>301234568</v>
@@ -2489,52 +2486,52 @@
         <v>123457</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H3">
         <v>46023</v>
       </c>
       <c r="I3" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="J3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L3">
         <v>46023</v>
       </c>
       <c r="M3" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="N3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P3">
         <v>46023</v>
       </c>
       <c r="Q3" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="R3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T3">
         <v>46023</v>
@@ -2542,7 +2539,7 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B4">
         <v>301234569</v>
@@ -2551,52 +2548,52 @@
         <v>123458</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H4">
         <v>46023</v>
       </c>
       <c r="I4" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J4" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K4" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L4">
         <v>46023</v>
       </c>
       <c r="M4" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="N4" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O4" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P4">
         <v>46023</v>
       </c>
       <c r="Q4" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="R4" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S4" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T4">
         <v>46023</v>
@@ -2604,7 +2601,7 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="B5">
         <v>301234570</v>
@@ -2613,52 +2610,52 @@
         <v>123459</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G5" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H5">
         <v>46023</v>
       </c>
       <c r="I5" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K5" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L5">
         <v>46023</v>
       </c>
       <c r="M5" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="N5" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O5" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P5">
         <v>46023</v>
       </c>
       <c r="Q5" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="R5" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S5" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T5">
         <v>46023</v>
@@ -2666,7 +2663,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="B6">
         <v>301234571</v>
@@ -2675,52 +2672,52 @@
         <v>123460</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H6">
         <v>46023</v>
       </c>
       <c r="I6" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="J6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L6">
         <v>46023</v>
       </c>
       <c r="M6" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="N6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P6">
         <v>46023</v>
       </c>
       <c r="Q6" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="R6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T6">
         <v>46023</v>
@@ -2728,7 +2725,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B7">
         <v>301234572</v>
@@ -2737,52 +2734,52 @@
         <v>123461</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G7" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H7">
         <v>46023</v>
       </c>
       <c r="I7" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="J7" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K7" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L7">
         <v>46023</v>
       </c>
       <c r="M7" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="N7" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O7" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P7">
         <v>46023</v>
       </c>
       <c r="Q7" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="R7" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S7" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T7">
         <v>46023</v>
@@ -2790,7 +2787,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="B8">
         <v>301234573</v>
@@ -2799,52 +2796,52 @@
         <v>123462</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H8">
         <v>46023</v>
       </c>
       <c r="I8" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="J8" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K8" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L8">
         <v>46023</v>
       </c>
       <c r="M8" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="N8" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O8" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P8">
         <v>46023</v>
       </c>
       <c r="Q8" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="R8" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S8" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T8">
         <v>46023</v>
@@ -2852,7 +2849,7 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="B9">
         <v>301234574</v>
@@ -2861,52 +2858,52 @@
         <v>123463</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H9">
         <v>46023</v>
       </c>
       <c r="I9" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="J9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L9">
         <v>46023</v>
       </c>
       <c r="M9" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="N9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P9">
         <v>46023</v>
       </c>
       <c r="Q9" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="R9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T9">
         <v>46023</v>
@@ -2914,7 +2911,7 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="B10">
         <v>301234575</v>
@@ -2923,52 +2920,52 @@
         <v>123464</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H10">
         <v>46023</v>
       </c>
       <c r="I10" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="J10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L10">
         <v>46023</v>
       </c>
       <c r="M10" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="N10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P10">
         <v>46023</v>
       </c>
       <c r="Q10" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="R10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T10">
         <v>46023</v>
@@ -2976,7 +2973,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="B11">
         <v>301234576</v>
@@ -2985,52 +2982,52 @@
         <v>123465</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H11">
         <v>46023</v>
       </c>
       <c r="I11" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="J11" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K11" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L11">
         <v>46023</v>
       </c>
       <c r="M11" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="N11" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O11" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P11">
         <v>46023</v>
       </c>
       <c r="Q11" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="R11" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S11" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T11">
         <v>46023</v>
@@ -3038,7 +3035,7 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="B12">
         <v>301234577</v>
@@ -3047,52 +3044,52 @@
         <v>123466</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E12" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H12">
         <v>46023</v>
       </c>
       <c r="I12" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="J12" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K12" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L12">
         <v>46023</v>
       </c>
       <c r="M12" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="N12" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O12" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P12">
         <v>46023</v>
       </c>
       <c r="Q12" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="R12" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S12" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T12">
         <v>46023</v>
@@ -3100,7 +3097,7 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B13">
         <v>301234578</v>
@@ -3109,52 +3106,52 @@
         <v>123467</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="F13" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H13">
         <v>46023</v>
       </c>
       <c r="I13" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="J13" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K13" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L13">
         <v>46023</v>
       </c>
       <c r="M13" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="N13" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O13" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P13">
         <v>46023</v>
       </c>
       <c r="Q13" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="R13" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S13" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T13">
         <v>46023</v>
@@ -3162,7 +3159,7 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="B14">
         <v>301234579</v>
@@ -3171,52 +3168,52 @@
         <v>123468</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H14">
         <v>46023</v>
       </c>
       <c r="I14" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="J14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L14">
         <v>46023</v>
       </c>
       <c r="M14" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="N14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P14">
         <v>46023</v>
       </c>
       <c r="Q14" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="R14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T14">
         <v>46023</v>
@@ -3224,7 +3221,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="B15">
         <v>301234580</v>
@@ -3233,52 +3230,52 @@
         <v>123469</v>
       </c>
       <c r="D15" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="F15" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H15">
         <v>46023</v>
       </c>
       <c r="I15" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="J15" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K15" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L15">
         <v>46023</v>
       </c>
       <c r="M15" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="N15" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O15" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P15">
         <v>46023</v>
       </c>
       <c r="Q15" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="R15" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S15" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T15">
         <v>46023</v>
@@ -3286,7 +3283,7 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="B16">
         <v>301234581</v>
@@ -3295,52 +3292,52 @@
         <v>123470</v>
       </c>
       <c r="D16" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E16" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G16" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H16">
         <v>46023</v>
       </c>
       <c r="I16" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K16" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L16">
         <v>46023</v>
       </c>
       <c r="M16" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="N16" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O16" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P16">
         <v>46023</v>
       </c>
       <c r="Q16" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="R16" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S16" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T16">
         <v>46023</v>
@@ -3348,7 +3345,7 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="B17">
         <v>301234582</v>
@@ -3357,52 +3354,52 @@
         <v>123471</v>
       </c>
       <c r="D17" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="E17" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H17">
         <v>46023</v>
       </c>
       <c r="I17" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="J17" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K17" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L17">
         <v>46023</v>
       </c>
       <c r="M17" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="N17" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O17" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P17">
         <v>46023</v>
       </c>
       <c r="Q17" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="R17" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S17" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T17">
         <v>46023</v>
@@ -3410,7 +3407,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="B18">
         <v>301234583</v>
@@ -3419,52 +3416,52 @@
         <v>123472</v>
       </c>
       <c r="D18" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="E18" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="F18" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G18" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H18">
         <v>46023</v>
       </c>
       <c r="I18" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="J18" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K18" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L18">
         <v>46023</v>
       </c>
       <c r="M18" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="N18" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O18" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P18">
         <v>46023</v>
       </c>
       <c r="Q18" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="R18" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S18" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T18">
         <v>46023</v>
@@ -3472,7 +3469,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B19">
         <v>301234584</v>
@@ -3481,52 +3478,52 @@
         <v>123473</v>
       </c>
       <c r="D19" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="E19" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="F19" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G19" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H19">
         <v>46023</v>
       </c>
       <c r="I19" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="J19" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K19" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L19">
         <v>46023</v>
       </c>
       <c r="M19" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="N19" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O19" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P19">
         <v>46023</v>
       </c>
       <c r="Q19" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="R19" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S19" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T19">
         <v>46023</v>
@@ -3534,7 +3531,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="B20">
         <v>301234585</v>
@@ -3543,52 +3540,52 @@
         <v>123474</v>
       </c>
       <c r="D20" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="E20" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G20" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H20">
         <v>46023</v>
       </c>
       <c r="I20" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="J20" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K20" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L20">
         <v>46023</v>
       </c>
       <c r="M20" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="N20" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O20" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P20">
         <v>46023</v>
       </c>
       <c r="Q20" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="R20" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S20" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T20">
         <v>46023</v>
@@ -3596,7 +3593,7 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="B21">
         <v>301234586</v>
@@ -3605,52 +3602,52 @@
         <v>123475</v>
       </c>
       <c r="D21" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="E21" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H21">
         <v>46023</v>
       </c>
       <c r="I21" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="J21" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K21" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L21">
         <v>46023</v>
       </c>
       <c r="M21" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="N21" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O21" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P21">
         <v>46023</v>
       </c>
       <c r="Q21" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="R21" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S21" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T21">
         <v>46023</v>
@@ -3658,7 +3655,7 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="B22">
         <v>301234587</v>
@@ -3667,52 +3664,52 @@
         <v>123476</v>
       </c>
       <c r="D22" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E22" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H22">
         <v>46023</v>
       </c>
       <c r="I22" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K22" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L22">
         <v>46023</v>
       </c>
       <c r="M22" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="N22" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O22" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P22">
         <v>46023</v>
       </c>
       <c r="Q22" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="R22" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S22" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T22">
         <v>46023</v>
@@ -3720,7 +3717,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="B23">
         <v>301234588</v>
@@ -3729,52 +3726,52 @@
         <v>123477</v>
       </c>
       <c r="D23" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="E23" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="F23" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H23">
         <v>46023</v>
       </c>
       <c r="I23" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="J23" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K23" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L23">
         <v>46023</v>
       </c>
       <c r="M23" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="N23" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O23" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P23">
         <v>46023</v>
       </c>
       <c r="Q23" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="R23" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S23" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T23">
         <v>46023</v>
@@ -3782,7 +3779,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="B24">
         <v>301234589</v>
@@ -3791,52 +3788,52 @@
         <v>123478</v>
       </c>
       <c r="D24" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="E24" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="F24" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G24" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H24">
         <v>46023</v>
       </c>
       <c r="I24" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="J24" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K24" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L24">
         <v>46023</v>
       </c>
       <c r="M24" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="N24" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O24" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P24">
         <v>46023</v>
       </c>
       <c r="Q24" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="R24" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S24" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T24">
         <v>46023</v>
@@ -3844,7 +3841,7 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="B25">
         <v>301234590</v>
@@ -3853,52 +3850,52 @@
         <v>123479</v>
       </c>
       <c r="D25" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="E25" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H25">
         <v>46023</v>
       </c>
       <c r="I25" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="J25" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K25" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L25">
         <v>46023</v>
       </c>
       <c r="M25" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="N25" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O25" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P25">
         <v>46023</v>
       </c>
       <c r="Q25" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="R25" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S25" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T25">
         <v>46023</v>
@@ -3906,7 +3903,7 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="B26">
         <v>301234591</v>
@@ -3915,52 +3912,52 @@
         <v>123480</v>
       </c>
       <c r="D26" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="E26" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G26" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H26">
         <v>46023</v>
       </c>
       <c r="I26" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="J26" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K26" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L26">
         <v>46023</v>
       </c>
       <c r="M26" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="N26" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O26" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P26">
         <v>46023</v>
       </c>
       <c r="Q26" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="R26" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S26" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T26">
         <v>46023</v>
@@ -3968,7 +3965,7 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B27">
         <v>301234592</v>
@@ -3977,52 +3974,52 @@
         <v>123481</v>
       </c>
       <c r="D27" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E27" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G27" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H27">
         <v>46023</v>
       </c>
       <c r="I27" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="J27" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K27" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L27">
         <v>46023</v>
       </c>
       <c r="M27" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="N27" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O27" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P27">
         <v>46023</v>
       </c>
       <c r="Q27" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="R27" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S27" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T27">
         <v>46023</v>
@@ -4030,7 +4027,7 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="B28">
         <v>301234593</v>
@@ -4039,52 +4036,52 @@
         <v>123482</v>
       </c>
       <c r="D28" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="E28" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="F28" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G28" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H28">
         <v>46023</v>
       </c>
       <c r="I28" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="J28" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K28" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L28">
         <v>46023</v>
       </c>
       <c r="M28" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="N28" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O28" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P28">
         <v>46023</v>
       </c>
       <c r="Q28" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="R28" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S28" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T28">
         <v>46023</v>
@@ -4092,7 +4089,7 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B29">
         <v>301234593</v>
@@ -4101,52 +4098,52 @@
         <v>123482</v>
       </c>
       <c r="D29" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="E29" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="F29" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G29" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H29">
         <v>46023</v>
       </c>
       <c r="I29" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="J29" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="K29" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L29">
         <v>46023</v>
       </c>
       <c r="M29" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="N29" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="O29" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="P29">
         <v>46023</v>
       </c>
       <c r="Q29" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="R29" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="S29" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T29">
         <v>46023</v>
